--- a/docs/superpowers/verification/exp75-evidence/文枢花名册-evidence.xlsx
+++ b/docs/superpowers/verification/exp75-evidence/文枢花名册-evidence.xlsx
@@ -375,7 +375,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>钟伟</t>
+          <t>TEST_EMP_NAME</t>
         </is>
       </c>
       <c r="H2" s="2"/>
@@ -385,12 +385,12 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>430981198311201111</t>
+          <t>TEST_ID_CARD_000000000000</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>15995408684</t>
+          <t>10000000000</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -430,7 +430,7 @@
       <c r="AO2" s="2"/>
       <c r="AP2" s="2" t="inlineStr">
         <is>
-          <t>6217231102004496773</t>
+          <t>TEST_BANK_ACCT_0000</t>
         </is>
       </c>
       <c r="AQ2" s="2"/>
